--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512478_ELIMINGRE14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512478_ELIMINGRE14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4625</v>
+        <v>6.846</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5672</v>
+        <v>5.9579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8953</v>
+        <v>0.8881</v>
       </c>
       <c r="G2" t="n">
-        <v>5.789</v>
+        <v>5.8043</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2714</v>
+        <v>2.2624</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5176</v>
+        <v>3.5419</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0628</v>
+        <v>5.2015</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9794</v>
+        <v>2.0321</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0834</v>
+        <v>3.1694</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7262</v>
+        <v>0.6028</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2919</v>
+        <v>0.2303</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4342</v>
+        <v>0.3725</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2073</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0955</v>
+        <v>0.1458</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1118</v>
+        <v>-0.9084</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9045</v>
+        <v>5.4132</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8591</v>
+        <v>3.2628</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0453</v>
+        <v>2.1504</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9091</v>
+        <v>5.0519</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7287</v>
+        <v>2.578</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1804</v>
+        <v>2.4739</v>
       </c>
       <c r="J3" t="n">
-        <v>3.461</v>
+        <v>5.2715</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9013</v>
+        <v>2.0937</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5598</v>
+        <v>3.1778</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4481</v>
+        <v>-0.2196</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8274</v>
+        <v>0.4843</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3794</v>
+        <v>-0.7039</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2003</v>
+        <v>-3.1158</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>2.7263</v>
       </c>
       <c r="S3" t="n">
-        <v>1.795</v>
+        <v>0.4197</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9385</v>
+        <v>0.4965</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1435</v>
+        <v>-0.0769</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5999</v>
+        <v>0.3311</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3401</v>
+        <v>0.6105</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1077</v>
+        <v>4.769</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0034</v>
+        <v>2.7705</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1044</v>
+        <v>1.9985</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0198</v>
+        <v>3.9127</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6095</v>
+        <v>2.7572</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4103</v>
+        <v>1.1556</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0866</v>
+        <v>3.5639</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0394</v>
+        <v>1.9834</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0472</v>
+        <v>1.5805</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0668</v>
+        <v>0.3488</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.7738</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6369</v>
+        <v>-0.4249</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2009</v>
+        <v>-1.1684</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8008</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.852</v>
+        <v>0.6878</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4822</v>
+        <v>0.706</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3698</v>
+        <v>-0.0182</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3401</v>
+        <v>-0.6105</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5999</v>
+        <v>-0.3311</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0151</v>
+        <v>2.8476</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6143</v>
+        <v>0.188</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6294</v>
+        <v>2.6596</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4936</v>
+        <v>1.4779</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5806</v>
+        <v>0.5393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.913</v>
+        <v>0.9387</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6893</v>
+        <v>0.8212</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0818</v>
+        <v>0.1155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6075</v>
+        <v>0.7057</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8043</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4988</v>
+        <v>0.4238</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3055</v>
+        <v>0.233</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0781</v>
+        <v>-0.2672</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4822</v>
+        <v>0.06</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5959</v>
+        <v>-0.3272</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9913</v>
+        <v>2.5616</v>
       </c>
       <c r="E6" t="n">
-        <v>0.045</v>
+        <v>0.7903</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9463</v>
+        <v>1.7713</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2787</v>
+        <v>1.2148</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1192</v>
+        <v>-0.1792</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3979</v>
+        <v>1.394</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6237</v>
+        <v>0.6778</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.618</v>
+        <v>-0.6029</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2417</v>
+        <v>1.2808</v>
       </c>
       <c r="M6" t="n">
-        <v>0.655</v>
+        <v>0.537</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4988</v>
+        <v>0.4238</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1562</v>
+        <v>0.1132</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.827</v>
+        <v>-0.2317</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8379</v>
+        <v>-0.2196</v>
       </c>
       <c r="U6" t="n">
-        <v>0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1398</v>
+        <v>2.1626</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6103</v>
+        <v>1.8415</v>
       </c>
       <c r="E7" t="n">
-        <v>0.384</v>
+        <v>0.7251</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2264</v>
+        <v>1.1164</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0555</v>
+        <v>1.0603</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1825</v>
+        <v>0.1621</v>
       </c>
       <c r="I7" t="n">
-        <v>0.873</v>
+        <v>0.8981</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6418</v>
+        <v>0.6734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4137</v>
+        <v>0.3869</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2454</v>
+        <v>0.0023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2578</v>
+        <v>0.0517</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0124</v>
+        <v>-0.0494</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6296</v>
+        <v>1.6205</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9817</v>
+        <v>-0.6524</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6113</v>
+        <v>2.2729</v>
       </c>
       <c r="G8" t="n">
-        <v>0.351</v>
+        <v>0.3626</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3861</v>
+        <v>0.4342</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.035</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5889</v>
+        <v>-0.427</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1127</v>
+        <v>0.0104</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4761</v>
+        <v>-0.4374</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9399</v>
+        <v>0.7897</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4988</v>
+        <v>0.4238</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4411</v>
+        <v>0.3659</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6408</v>
+        <v>-0.7169</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0313</v>
+        <v>-0.0064</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6095</v>
+        <v>-0.7104</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
-        <v>1.639</v>
+        <v>1.7284</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0794</v>
+        <v>-0.7523</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1972</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1178</v>
+        <v>-0.026</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0685</v>
+        <v>-0.604</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0825</v>
+        <v>-0.7369</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1511</v>
+        <v>0.1329</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6525</v>
+        <v>-0.6645</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0164</v>
+        <v>-0.6645</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6361</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4161</v>
+        <v>0.0605</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0989</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.515</v>
+        <v>0.1329</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3295</v>
+        <v>-0.1484</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1961</v>
+        <v>-0.0618</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1334</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8502</v>
+        <v>-0.8385</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7677</v>
+        <v>-1.5677</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9175</v>
+        <v>0.7292</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5723</v>
+        <v>-1.0979</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2992</v>
+        <v>0.0595</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2731</v>
+        <v>-1.1574</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0438</v>
+        <v>-0.5533</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.598</v>
+        <v>0.0463</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6418</v>
+        <v>-0.5995</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6161</v>
+        <v>-0.5446</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2989</v>
+        <v>0.0132</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9149</v>
+        <v>-0.5578</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6005</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3226</v>
+        <v>0.5641</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3891</v>
+        <v>0.6534</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9334</v>
+        <v>-0.0893</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8519</v>
+        <v>-1.3209</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8069</v>
+        <v>-1.7849</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.045</v>
+        <v>0.464</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6067</v>
+        <v>-2.5832</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7423</v>
+        <v>-0.8698</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1356</v>
+        <v>-1.7134</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.678</v>
+        <v>-1.6399</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.678</v>
+        <v>-0.3514</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.2885</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0713</v>
+        <v>-0.9433</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0643</v>
+        <v>-0.5184</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1356</v>
+        <v>-0.4249</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2452</v>
+        <v>0.126</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1289</v>
+        <v>0.5492</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1163</v>
+        <v>-0.4232</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.9416</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3879</v>
+        <v>-1.5581</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9729</v>
+        <v>-2.0009</v>
       </c>
       <c r="F12" t="n">
-        <v>0.585</v>
+        <v>0.4427</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5733</v>
+        <v>-0.6541</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8779</v>
+        <v>-0.3639</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6954</v>
+        <v>-0.2902</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7505</v>
+        <v>0.0905</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4345</v>
+        <v>-0.5824</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.316</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8229</v>
+        <v>-0.7446</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4435</v>
+        <v>0.2185</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3794</v>
+        <v>-0.9631</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-2.1421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0454</v>
+        <v>0.6539</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5181</v>
+        <v>0.0508</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4727</v>
+        <v>0.6031</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5494</v>
+        <v>-3.5768</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6473</v>
+        <v>-4.0919</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0979</v>
+        <v>0.5151</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6524</v>
+        <v>-4.5768</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0565</v>
+        <v>-1.9914</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5958</v>
+        <v>-2.5853</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.4227</v>
+        <v>-3.24</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1485</v>
+        <v>-2.0165</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2741</v>
+        <v>-1.2235</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2297</v>
+        <v>-1.3367</v>
       </c>
       <c r="N13" t="n">
-        <v>0.092</v>
+        <v>0.0251</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3217</v>
+        <v>-1.3618</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5028</v>
+        <v>0.4158</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2244</v>
+        <v>0.1218</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7272</v>
+        <v>0.2939</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.00220000000001</v>
+        <v>17.8528</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1293</v>
+        <v>2.870500000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>17.1316</v>
+        <v>14.9822</v>
       </c>
       <c r="G14" t="n">
-        <v>9.423500000000004</v>
+        <v>9.368500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7462</v>
+        <v>4.6515</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6774</v>
+        <v>4.7173</v>
       </c>
       <c r="J14" t="n">
-        <v>8.516399999999997</v>
+        <v>9.775099999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>1.435800000000001</v>
+        <v>2.1048</v>
       </c>
       <c r="L14" t="n">
-        <v>7.080899999999999</v>
+        <v>7.670500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9068999999999996</v>
+        <v>-0.4063</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3103</v>
+        <v>2.5469</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.4035</v>
+        <v>-2.9531</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0002</v>
+        <v>0.9735</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.0045</v>
+        <v>-15.579</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0049</v>
+        <v>16.5526</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1005</v>
+        <v>0.7428000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5015999999999998</v>
+        <v>2.5474</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.602100000000001</v>
+        <v>-1.8045</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6792</v>
+        <v>6.767499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>5.857200000000001</v>
+        <v>6.126799999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8219000000000003</v>
+        <v>0.6404</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1669</v>
+        <v>2.52</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9427</v>
+        <v>1.6002</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2241</v>
+        <v>0.9198</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5624</v>
+        <v>1.5553</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7398</v>
+        <v>-0.7595</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3022</v>
+        <v>2.3148</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5853</v>
+        <v>1.6881</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2963</v>
+        <v>-0.2411</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.023</v>
+        <v>-0.1328</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4435</v>
+        <v>-0.5184</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1237</v>
+        <v>-0.7441</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7023</v>
+        <v>-0.1726</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4214</v>
+        <v>-0.5715</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3278</v>
+        <v>0.3457</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X15" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6934</v>
+        <v>1.6593</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2622</v>
+        <v>0.7823</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4312</v>
+        <v>0.877</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0847</v>
+        <v>5.0899</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1445</v>
+        <v>2.1511</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9402</v>
+        <v>2.9387</v>
       </c>
       <c r="J16" t="n">
-        <v>3.423</v>
+        <v>3.5436</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5814</v>
+        <v>1.655</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8416</v>
+        <v>1.8887</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6617</v>
+        <v>1.5462</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5631</v>
+        <v>0.4961</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0985</v>
+        <v>1.0501</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8597</v>
+        <v>-0.8599</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.6193</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1005</v>
+        <v>-0.2407</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.3315</v>
+        <v>-2.3759</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3315</v>
+        <v>-2.3759</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7426</v>
+        <v>0.6079</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8108</v>
+        <v>0.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0682</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6172</v>
+        <v>0.6079</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5977</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0194</v>
+        <v>0.6079</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5161</v>
+        <v>0.6079</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.276</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7599</v>
+        <v>0.6079</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.101</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3217</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7793</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2791</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0671</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5999</v>
+        <v>-0.3239</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5999</v>
+        <v>-0.1282</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.1957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5999</v>
+        <v>-1.6689</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.6087</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5999</v>
+        <v>-0.0602</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5999</v>
+        <v>-0.4769</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.2469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5999</v>
+        <v>0.77</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.192</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.3618</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.8302</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.3198</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.2506</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.176</v>
+        <v>-0.5553</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2455</v>
+        <v>-0.026</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0696</v>
+        <v>-0.5294</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2306</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0425</v>
+        <v>-0.1155</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2731</v>
+        <v>-0.7277</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5362</v>
+        <v>0.9791</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0218</v>
+        <v>-0.2129</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5580000000000001</v>
+        <v>1.192</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3057</v>
+        <v>-1.8222</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0207</v>
+        <v>0.0974</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2849</v>
+        <v>-1.9197</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2003</v>
+        <v>1.5579</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0134</v>
+        <v>0.2626</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.509</v>
+        <v>-0.0314</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5044</v>
+        <v>0.2939</v>
       </c>
       <c r="V19" t="n">
-        <v>0.068</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.068</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9609</v>
+        <v>-0.9119</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.669</v>
+        <v>-1.9435</v>
       </c>
       <c r="F20" t="n">
-        <v>0.708</v>
+        <v>1.0317</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0653</v>
+        <v>-0.2718</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0066</v>
+        <v>0.0184</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0719</v>
+        <v>-0.2902</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2632</v>
+        <v>-0.489</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2433</v>
+        <v>0.0539</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5065</v>
+        <v>-0.5429</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8021</v>
+        <v>0.2172</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2366</v>
+        <v>-0.0355</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5655</v>
+        <v>0.2527</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0009</v>
+        <v>-1.1684</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0006</v>
+        <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8449</v>
+        <v>-0.7063</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1843</v>
+        <v>-0.2861</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0291</v>
+        <v>-0.4202</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2598</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7794</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5196</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1179</v>
+        <v>-1.861</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4334</v>
+        <v>-1.7595</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6845</v>
+        <v>-0.1015</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.831</v>
+        <v>-2.0083</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0818</v>
+        <v>1.0145</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7492</v>
+        <v>-3.0228</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8493000000000001</v>
+        <v>-0.0295</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2381</v>
+        <v>1.3394</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0875</v>
+        <v>-1.3689</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6803</v>
+        <v>-1.9788</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1563</v>
+        <v>-0.3249</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8367</v>
+        <v>-1.6539</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6005</v>
+        <v>1.9474</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3674</v>
+        <v>0.8415</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2824</v>
+        <v>0.3526</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.4889</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5196</v>
+        <v>0.2795</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8384</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5897</v>
+        <v>-2.6585</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4948</v>
+        <v>-0.6493</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0949</v>
+        <v>-2.0092</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7134</v>
+        <v>-1.7148</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9623</v>
+        <v>-0.9627</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7511</v>
+        <v>-0.7521</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1874</v>
+        <v>0.293</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3763</v>
+        <v>-0.3232</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5637</v>
+        <v>0.6163</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9009</v>
+        <v>-2.0078</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3149</v>
+        <v>-1.3684</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0764</v>
+        <v>-0.1384</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5181</v>
+        <v>0.2261</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5944</v>
+        <v>-0.3646</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.388</v>
+        <v>-3.7466</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.232</v>
+        <v>-3.9552</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.156</v>
+        <v>0.2086</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9204</v>
+        <v>-4.226</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1661</v>
+        <v>-2.7283</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0866</v>
+        <v>-1.4977</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7688</v>
+        <v>-4.0854</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5453</v>
+        <v>-2.8863</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3141</v>
+        <v>-1.1991</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1516</v>
+        <v>-0.1406</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3791</v>
+        <v>0.158</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7725</v>
+        <v>-0.2986</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.401</v>
+        <v>2.1421</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.2015</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8005</v>
+        <v>2.1421</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2938</v>
+        <v>0.1027</v>
       </c>
       <c r="T23" t="n">
-        <v>3.179</v>
+        <v>0.1302</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8852</v>
+        <v>-0.0275</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3604</v>
+        <v>-1.7654</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.4407</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0803</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4627</v>
+        <v>-5.0612</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9694</v>
+        <v>-3.808</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4934</v>
+        <v>-1.2531</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.9844</v>
+        <v>-3.9964</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9253</v>
+        <v>-1.8693</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0591</v>
+        <v>-2.1271</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1688</v>
+        <v>-1.0149</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4887</v>
+        <v>-1.3391</v>
       </c>
       <c r="L24" t="n">
-        <v>0.32</v>
+        <v>0.3242</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8157</v>
+        <v>-2.9814</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4366</v>
+        <v>-0.5302</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.3791</v>
+        <v>-2.4513</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7941</v>
+        <v>1.1737</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9136</v>
+        <v>0.3837</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.872</v>
+        <v>-0.8754</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1918</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5096</v>
+        <v>-5.6665</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7031</v>
+        <v>-5.7029</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1935</v>
+        <v>0.0364</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.308</v>
+        <v>-1.8924</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.7989</v>
+        <v>0.2084</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5091</v>
+        <v>-2.1008</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2987</v>
+        <v>-0.6097</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.0265</v>
+        <v>0.6544</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2722</v>
+        <v>-1.264</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-1.2828</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2276</v>
+        <v>-0.446</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2369</v>
+        <v>-0.8368</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2006</v>
+        <v>-3.3105</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-5.0631</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2006</v>
+        <v>1.7526</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6706</v>
+        <v>0.8606</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4044</v>
+        <v>1.3456</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2662</v>
+        <v>-0.485</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7316</v>
+        <v>-1.3242</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-1.3758</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7316</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.002</v>
+        <v>-15.9977</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.1316</v>
+        <v>-14.9822</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1294</v>
+        <v>-1.0154</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.423300000000001</v>
+        <v>-9.3687</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.7461</v>
+        <v>-4.651599999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.6772</v>
+        <v>-4.7172</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9068999999999994</v>
+        <v>0.4063</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.3101</v>
+        <v>-2.5468</v>
       </c>
       <c r="L26" t="n">
-        <v>2.4034</v>
+        <v>2.953399999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.516500000000001</v>
+        <v>-9.775</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4358</v>
+        <v>-2.1047</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.081</v>
+        <v>-7.670500000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.0004</v>
+        <v>-0.9736000000000002</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0049</v>
+        <v>-16.5524</v>
       </c>
       <c r="R26" t="n">
-        <v>16.0047</v>
+        <v>15.579</v>
       </c>
       <c r="S26" t="n">
-        <v>1.1007</v>
+        <v>1.1122</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6021</v>
+        <v>1.8043</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5014000000000001</v>
+        <v>-0.6924000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.6791</v>
+        <v>-6.7674</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.8219000000000002</v>
+        <v>-0.6404999999999997</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.857200000000001</v>
+        <v>-6.127000000000002</v>
       </c>
     </row>
   </sheetData>
